--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>20/09 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>175</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>150</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>140</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>140</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>140</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>150</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>18/09 17:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>150</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>125</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>125</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>125</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>125</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>18/09 17:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>125</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>125</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>110</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>18/09 17:45</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>110</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45917.0675550137</v>
+        <v>45917.06755501158</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Spusu Vien</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Spusu Vienna Capitals – Black Wings LinzICE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19/09 17:15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+224%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45917.12279389503</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Presov – T</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Presov – TrencinSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45917.12279389503</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Munich</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EHC Munich – AugsbourgDEL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+123%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45917.12279389503</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Banska Bys</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Banska Bystrica – ZilinaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>19/09 15:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45917.12279389503</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>200</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45917.12279389503</v>
+        <v>45917.12279390046</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>150</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45917.12279389503</v>
+        <v>45917.12279390046</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>150</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45917.12279389503</v>
+        <v>45917.12279390046</v>
       </c>
     </row>
     <row r="30">
@@ -1715,23 +1709,66 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>140</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45917.12279390046</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Pardubi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HC Pardubice – HC OlomoucExtraliga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>+116%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>45917.12279389503</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+92,9%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45917.14592163086</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,23 +1752,246 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>140</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+92,9%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45917.14592163194</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Fehervar A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fehervar AV19 – HC Twk Innsbruck Die HaieICE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20/09 15:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45917.18407375935</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – BerlinDEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>+92,9%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>45917.14592163086</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45917.18407375935</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HIFK – Luk</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HIFK – LukkoFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>17/09 15:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+98,5%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45917.18407375935</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | SaiPa – Ta</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SaiPa – Tappara TampereFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>17/09 15:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+78,3%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45917.18407375935</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Jukurit – </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jukurit – Ilves TampereFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17/09 15:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+78,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45917.18407375935</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>20/09 15:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>175</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45917.18407375935</v>
+        <v>45917.18407376157</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>140</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45917.18407375935</v>
+        <v>45917.18407376157</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>140</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45917.18407375935</v>
+        <v>45917.18407376157</v>
       </c>
     </row>
     <row r="35">
@@ -1930,10 +1924,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>125</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1946,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45917.18407375935</v>
+        <v>45917.18407376157</v>
       </c>
     </row>
     <row r="36">
@@ -1975,23 +1967,111 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>125</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+78,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45917.18407376157</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SC Rappers</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SC Rapperswil-Jona Lakers – LausanneNational League A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19/09 17:45</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+78,1%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45917.22297094201</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Skellefteå</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Skellefteå AIK – Färjestad BKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>18/09 17:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>+78,2%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>45917.18407375935</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+76,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45917.22297094201</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>110</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45917.22297094201</v>
+        <v>45917.2229709375</v>
       </c>
     </row>
     <row r="38">
@@ -2055,23 +2053,66 @@
           <t>18/09 17:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>125</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+76,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45917.2229709375</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kladno – C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Kladno – Ceske BudejoviceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>+76,6%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>45917.22297094201</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+90,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45917.27213788486</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,23 +2096,201 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>125</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+90,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45917.27213788195</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nitra – Li</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Nitra – Liptovsky MikulasSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45917.30542433286</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kloten Fly</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Kloten Flyers – ZugSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/09 17:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+126%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45917.30542433286</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lowen Fran</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lowen Frankfurt – Dresdner EislowenDEL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18/09 17:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45917.30542433286</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Karlovy Va</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Karlovy Vary – Mountfield HKRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>+90,0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>45917.27213788486</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+87,3%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45917.30542433286</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>200</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45917.30542433286</v>
+        <v>45917.3054243287</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>140</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45917.30542433286</v>
+        <v>45917.3054243287</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>18/09 17:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>140</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45917.30542433286</v>
+        <v>45917.3054243287</v>
       </c>
     </row>
     <row r="43">
@@ -2274,23 +2268,156 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>125</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+87,3%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45917.3054243287</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HV71 – Bry</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HV71 – Brynäs IFSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>18/09 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+146%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45917.35288301684</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Linköpings</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Linköpings HC – Djurgårdens IFSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>18/09 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+98,7%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45917.35288301684</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – StraubingDEL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1,50%</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>+87,3%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>45917.30542433286</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+92,1%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45917.35288301684</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -2311,10 +2311,8 @@
           <t>18/09 17:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>175</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45917.35288301684</v>
+        <v>45917.35288302083</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>18/09 17:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>140</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45917.35288301684</v>
+        <v>45917.35288302083</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>125</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45917.35288301684</v>
+        <v>45917.35288302083</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,51 @@
         <v>45917.35288302083</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Salzbourg – EC VSVAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19/09 17:15</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+207%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45917.43163193724</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -2440,10 +2440,8 @@
           <t>19/09 17:15</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>200</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45917.43163193724</v>
+        <v>45917.43163193287</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2457,96 @@
         <v>45917.43163193287</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Iserlohn R</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Iserlohn Roosters – Nurnberg Ice TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45917.52993618242</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HK Poprad </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HK Poprad – HC KosiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+96,8%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45917.52993618242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -2483,10 +2483,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>150</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45917.52993618242</v>
+        <v>45917.52993618056</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>125</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45917.52993618242</v>
+        <v>45917.52993618056</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,6 +2543,96 @@
         <v>45917.52993618056</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Pioneers V</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pioneers Vorarlberg – BolzanoICE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+203%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45917.64088857069</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Spisska No</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spisska Nova Ves – Dukla MichalovceExtraliga</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19/09 15:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+120%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45917.64088857069</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -2569,10 +2569,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>200</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45917.64088857069</v>
+        <v>45917.64088857639</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>19/09 15:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>140</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45917.64088857069</v>
+        <v>45917.64088857639</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2629,51 @@
         <v>45917.64088857639</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Energie Ka</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Energie Karlovy Vary – Mountfield HKExtraliga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+87,5%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45917.72108101014</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>125</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,52 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45917.72108101014</v>
+        <v>45917.72108100694</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Wolfsburg GrizzlyAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+179%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45917.77158456463</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -2698,10 +2698,8 @@
           <t>19/09 17:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>200</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45917.77158456463</v>
+        <v>45917.77158456019</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2715,6 +2715,141 @@
         <v>45917.77158456019</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HKM AS Zvo</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HKM AS Zvolen – Slovan BratislavaExtraliga</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19/09 16:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+124%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45917.88752992774</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lugano – A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Lugano – AjoieSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19/09 17:45</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45917.88752992774</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Skelleftea</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Skelleftea AIK – Farjestads BKSHL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>18/09 17:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45917.88752992774</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-17.xlsx
+++ b/data/valuebets_database_2025-09-17.xlsx
@@ -2741,10 +2741,8 @@
           <t>19/09 16:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>150</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45917.88752992774</v>
+        <v>45917.88752993056</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>19/09 17:45</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>140</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45917.88752992774</v>
+        <v>45917.88752993056</v>
       </c>
     </row>
     <row r="56">
@@ -2831,10 +2827,8 @@
           <t>18/09 17:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>140</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2847,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45917.88752992774</v>
+        <v>45917.88752993056</v>
       </c>
     </row>
   </sheetData>
